--- a/Experiments.xlsx
+++ b/Experiments.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smu-my.sharepoint.com/personal/kh_nguyen_2025_mitb_smu_edu_sg/Documents/Data_Science/SMU/Study/Term 2/CS610 Applied ML/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95C4CE0D-2520-4E0B-A98D-599385999CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{95C4CE0D-2520-4E0B-A98D-599385999CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77CD6F80-6976-469B-986F-FAEA47A2BC10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3AEB3263-0B0E-46D1-87D0-7CDB5ACB019C}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="2" r:id="rId1"/>
-    <sheet name="Experiments" sheetId="1" r:id="rId2"/>
+    <sheet name="Experiments_full (2)" sheetId="4" r:id="rId2"/>
+    <sheet name="Experiments_full" sheetId="3" r:id="rId3"/>
+    <sheet name="Experiments" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
   <si>
     <t>D_MODEL</t>
   </si>
@@ -209,6 +211,18 @@
       <t xml:space="preserve"> train=1,400, val=300, test=300</t>
     </r>
   </si>
+  <si>
+    <t>Ex1</t>
+  </si>
+  <si>
+    <t>Ex2</t>
+  </si>
+  <si>
+    <t>Val Acc</t>
+  </si>
+  <si>
+    <t>ROC-AUC</t>
+  </si>
 </sst>
 </file>
 
@@ -216,7 +230,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -279,7 +293,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -307,6 +321,241 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>495301</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>2744</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>68052</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{627C7B62-A705-3D93-9FAB-B3DD9C07B330}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="495301" y="1648664"/>
+          <a:ext cx="7551419" cy="2259868"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>175758</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>349496</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABE423A4-5412-445E-47BF-CDD285B81AF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="525780" y="1638798"/>
+          <a:ext cx="7756136" cy="2232162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>555813</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C777FF2C-B198-5F8F-93AE-2628A1F4F53B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="4023360"/>
+          <a:ext cx="7878633" cy="2324100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1458</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>488117</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>64339</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7BFE7B8-51D4-FF48-471A-8160D4252F5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="556260" y="1647378"/>
+          <a:ext cx="7689017" cy="2257441"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>336765</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>64349</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6AD7F34-355F-D9C6-EEBE-A2345DB1AD72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="670560" y="4130040"/>
+          <a:ext cx="7423365" cy="2152229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -696,15 +945,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2361BB-17A0-4C3F-9B6A-2513337F59A8}">
-  <dimension ref="A1:I5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24A1F2F-805E-440C-9C1A-6E75956BA2C7}">
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="15.5546875" customWidth="1"/>
     <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -724,21 +975,30 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="O1">
+        <v>20260611</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>500</v>
+        <v>9219</v>
       </c>
       <c r="C2" s="2">
         <v>64</v>
@@ -752,16 +1012,28 @@
       <c r="F2" s="2">
         <v>0.1</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G2" s="2">
+        <v>0.3982</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.28710000000000002</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.98219999999999996</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.53939999999999999</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.77370000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>500</v>
+        <v>9219</v>
       </c>
       <c r="C3" s="2">
         <v>128</v>
@@ -778,13 +1050,15 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>500</v>
+        <v>9219</v>
       </c>
       <c r="C4" s="2">
         <v>64</v>
@@ -798,16 +1072,16 @@
       <c r="F4" s="2">
         <v>0.1</v>
       </c>
-      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>500</v>
+        <v>9219</v>
       </c>
       <c r="C5" s="2">
         <v>64</v>
@@ -821,11 +1095,375 @@
       <c r="F5" s="2">
         <v>0.3</v>
       </c>
-      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2399DC89-E2E3-449D-974C-947B56FF3DC3}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>500</v>
+      </c>
+      <c r="C2" s="2">
+        <v>64</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.40360000000000001</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.28760000000000002</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.57720000000000005</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.7863</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>500</v>
+      </c>
+      <c r="C3" s="2">
+        <v>128</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <v>0.78649999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>500</v>
+      </c>
+      <c r="C4" s="2">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>500</v>
+      </c>
+      <c r="C5" s="2">
+        <v>64</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2361BB-17A0-4C3F-9B6A-2513337F59A8}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>500</v>
+      </c>
+      <c r="C2" s="2">
+        <v>64</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.4667</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.71050000000000002</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.55879999999999996</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.63739999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>500</v>
+      </c>
+      <c r="C3" s="2">
+        <v>128</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.54169999999999996</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.37719999999999998</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.56889999999999996</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.81320000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>500</v>
+      </c>
+      <c r="C4" s="2">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>500</v>
+      </c>
+      <c r="C5" s="2">
+        <v>64</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c98a79ca-5a9a-4791-a243-f06afd67464d}" enabled="0" method="" siteId="{c98a79ca-5a9a-4791-a243-f06afd67464d}" removed="1"/>
+</clbl:labelList>
 </file>